--- a/data/dividends_info_20260925.xlsx
+++ b/data/dividends_info_20260925.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>45.64500045776367</v>
+        <v>45.10499954223633</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1971738396262675</v>
+        <v>0.19953442171244</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.07499694824219</v>
+        <v>63.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.075681955938852</v>
+        <v>1.094605147222557</v>
       </c>
       <c r="J3" t="n">
         <v>150</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.800000190734863</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6818181670401711</v>
+        <v>0.6607929570941081</v>
       </c>
       <c r="J4" t="n">
         <v>80</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45.65000152587891</v>
+        <v>45.10499954223633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1971522387550834</v>
+        <v>0.19953442171244</v>
       </c>
       <c r="J6" t="n">
         <v>80</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.075000047683716</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.710843288218411</v>
       </c>
       <c r="J7" t="n">
         <v>59</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.05999946594238</v>
+        <v>24.09000015258789</v>
       </c>
       <c r="I8" t="n">
-        <v>1.12219453862496</v>
+        <v>1.120797004108757</v>
       </c>
       <c r="J8" t="n">
         <v>59</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.44000053405762</v>
+        <v>24.42000007629395</v>
       </c>
       <c r="I9" t="n">
-        <v>2.41407523366386</v>
+        <v>2.416052408504088</v>
       </c>
       <c r="J9" t="n">
         <v>59</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.949999809265137</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I10" t="n">
-        <v>3.36134464556733</v>
+        <v>3.378378334839559</v>
       </c>
       <c r="J10" t="n">
         <v>52</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8.5</v>
+        <v>8.850000381469727</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7058823529411764</v>
+        <v>0.6779660724719172</v>
       </c>
       <c r="J12" t="n">
         <v>24</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.05999946594238</v>
+        <v>24.09000015258789</v>
       </c>
       <c r="I16" t="n">
-        <v>1.12219453862496</v>
+        <v>1.120797004108757</v>
       </c>
       <c r="J16" t="n">
         <v>-4</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.906000018119812</v>
+        <v>1.914999961853027</v>
       </c>
       <c r="I17" t="n">
-        <v>2.990556110079583</v>
+        <v>2.976501364775204</v>
       </c>
       <c r="J17" t="n">
         <v>-4</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>45.65000152587891</v>
+        <v>45.10499954223633</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1971522387550834</v>
+        <v>0.19953442171244</v>
       </c>
       <c r="J18" t="n">
         <v>-4</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>93.5</v>
+        <v>94.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.422459893048128</v>
+        <v>1.407407407407408</v>
       </c>
       <c r="J19" t="n">
         <v>-4</v>
@@ -1392,7 +1392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2401,7 +2401,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2418,7 +2418,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2673,7 +2673,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2690,7 +2690,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2724,7 +2724,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2741,7 +2741,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2775,7 +2775,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2792,7 +2792,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2809,7 +2809,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2962,7 +2962,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3013,7 +3013,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3030,7 +3030,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3047,7 +3047,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3064,7 +3064,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3183,7 +3183,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3217,7 +3217,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3234,7 +3234,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3329,14 +3329,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3431,14 +3431,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3448,14 +3448,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3472,7 +3472,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3506,7 +3506,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3523,7 +3523,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3584,14 +3584,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3625,7 +3625,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3635,14 +3635,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3676,7 +3676,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3693,7 +3693,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3710,7 +3710,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3727,7 +3727,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3761,7 +3761,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3778,7 +3778,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3812,7 +3812,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3829,7 +3829,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3863,7 +3863,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3880,7 +3880,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3924,14 +3924,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3982,7 +3982,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4009,14 +4009,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4033,7 +4033,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4067,7 +4067,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4084,7 +4084,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4111,14 +4111,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4203,7 +4203,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4213,14 +4213,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4237,7 +4237,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4254,7 +4254,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4288,7 +4288,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4305,7 +4305,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4339,7 +4339,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4356,7 +4356,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4373,7 +4373,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4407,7 +4407,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4424,7 +4424,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4458,7 +4458,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4509,7 +4509,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4526,7 +4526,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4577,7 +4577,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4594,7 +4594,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4611,7 +4611,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4645,7 +4645,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4781,7 +4781,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4791,14 +4791,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4808,14 +4808,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4842,14 +4842,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4859,14 +4859,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4893,14 +4893,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5063,14 +5063,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5087,7 +5087,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5148,19 +5148,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5172,236 +5172,66 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Industrie De Nora S.p.A.</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
